--- a/samples/incoming_inspection/수입검사_미래부품.xlsx
+++ b/samples/incoming_inspection/수입검사_미래부품.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -54,7 +51,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -435,61 +432,91 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>검사일자</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>업체명</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>품목코드</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>품목명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LOT No</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>검사결과</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>입고량</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>샘플수량</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>불량수</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>검사일자</t>
+          <t>2026.09.02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>업체명</t>
+          <t>(주)미래부품</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>품목코드</t>
+          <t>HB-1001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>품목명</t>
+          <t>브라켓 A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LOT No</t>
+          <t>MR260902-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>검사결과</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>입고량</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>샘플수량</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>불량수</t>
-        </is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -505,17 +532,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HB-1001</t>
+          <t>HB-2010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>브라켓 A</t>
+          <t>샤프트 20mm</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MR260902-01</t>
+          <t>MR260902-02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -524,10 +551,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -544,19 +571,14 @@
           <t>(주)미래부품</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HB-2010</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>샤프트 20mm</t>
+          <t>브라켓 B</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MR260902-02</t>
+          <t>MR260902-03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -568,7 +590,7 @@
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -577,7 +599,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026.09.02</t>
+          <t>2026.09.03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,29 +607,34 @@
           <t>(주)미래부품</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HB-6300</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>브라켓 B</t>
+          <t>스프링 와셔</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MR260902-03</t>
+          <t>MR260903-04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>합격</t>
+          <t>불합격</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -623,32 +650,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HB-6300</t>
+          <t>HB-5200</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>스프링 와셔</t>
+          <t>볼트 M6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MR260903-04</t>
+          <t>MR260903-05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>불합격</t>
+          <t>합격</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
         <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -664,29 +691,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HB-5200</t>
+          <t>HB-2010</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>볼트 M6</t>
+          <t>샤프트 20mm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MR260903-05</t>
+          <t>MR260903-06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>합격</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -695,7 +722,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026.09.03</t>
+          <t>2026.13.02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -705,38 +732,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HB-2010</t>
+          <t>HB-5200</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>샤프트 20mm</t>
+          <t>볼트 M6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MR260903-06</t>
+          <t>MR260904-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>불합격</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026.13.02</t>
+          <t>2026.09.04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -746,32 +773,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HB-5200</t>
+          <t>HB-1002</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>볼트 M6</t>
+          <t>브라켓 B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MR260904-07</t>
+          <t>MR260904-08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>불합격</t>
+          <t>합격</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -787,38 +814,38 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HB-1002</t>
+          <t>HB-5201</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>브라켓 B</t>
+          <t>너트 M6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MR260904-08</t>
+          <t>MR260904-09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>합격</t>
+          <t>불합격</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H10" t="n">
         <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026.09.04</t>
+          <t>2026.09.05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -828,17 +855,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HB-5201</t>
+          <t>HB-2010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>너트 M6</t>
+          <t>샤프트 20mm</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MR260904-09</t>
+          <t>MR260905-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -849,8 +876,10 @@
       <c r="G11" t="n">
         <v>300</v>
       </c>
-      <c r="H11" t="n">
-        <v>13</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>20EA</t>
+        </is>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -869,60 +898,58 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HB-2010</t>
+          <t>HB-3100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>샤프트 20mm</t>
+          <t>하우징 커버</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MR260905-10</t>
+          <t>MR260905-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>불합격</t>
+          <t>합격</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>300</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>20EA</t>
-        </is>
+      <c r="H12" t="n">
+        <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026.09.05</t>
+          <t>2026.09.01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(주)미래부품</t>
+          <t>대성정공</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HB-3100</t>
+          <t>HB-1001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>하우징 커버</t>
+          <t>브라켓 A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MR260905-11</t>
+          <t>DS260901-02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -931,53 +958,12 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026.09.01</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>대성정공</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>HB-1001</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>브라켓 A</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>DS260901-02</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>200</v>
-      </c>
-      <c r="H14" t="n">
-        <v>13</v>
-      </c>
-      <c r="I14" t="n">
         <v>0</v>
       </c>
     </row>
